--- a/experiment_results/wedos_grid/rtt_bursts_S3_atk5pct_wu500000_stage1a_rep1.xlsx
+++ b/experiment_results/wedos_grid/rtt_bursts_S3_atk5pct_wu500000_stage1a_rep1.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>997278</t>
+          <t>564343</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1367402</t>
+          <t>803058</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1724654</t>
+          <t>921596</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2072278</t>
+          <t>1150682</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2429850</t>
+          <t>1279168</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2523414</t>
+          <t>1244246</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2470293</t>
+          <t>1226047</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2430618</t>
+          <t>1204571</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2337170</t>
+          <t>1132599</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2346909</t>
+          <t>1214310</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2345273</t>
+          <t>1130964</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2189682</t>
+          <t>1058718</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2167318</t>
+          <t>1108600</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2105803</t>
+          <t>997202</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1862808</t>
+          <t>865606</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1729290</t>
+          <t>863685</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1727369</t>
+          <t>863685</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
